--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/50.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/50.xlsx
@@ -426,13 +426,13 @@
         <v>-13.71010664399527</v>
       </c>
       <c r="E2">
-        <v>-18.36990971714767</v>
+        <v>-14.87717943609529</v>
       </c>
       <c r="F2">
-        <v>1.372270807127945</v>
+        <v>2.285552495653622</v>
       </c>
       <c r="G2">
-        <v>-14.86769516612106</v>
+        <v>-14.05754326370204</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.21446795608926</v>
       </c>
       <c r="E3">
-        <v>-18.91086549220659</v>
+        <v>-15.71469111259227</v>
       </c>
       <c r="F3">
-        <v>1.452501503558688</v>
+        <v>2.304899844713407</v>
       </c>
       <c r="G3">
-        <v>-14.23797834925536</v>
+        <v>-13.75385884211915</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.64066446029025</v>
       </c>
       <c r="E4">
-        <v>-18.97263205102944</v>
+        <v>-16.34978357553975</v>
       </c>
       <c r="F4">
-        <v>2.238123491638934</v>
+        <v>2.211055758385057</v>
       </c>
       <c r="G4">
-        <v>-14.09956972475749</v>
+        <v>-13.00033921137056</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.03795951702761</v>
       </c>
       <c r="E5">
-        <v>-18.02999013626708</v>
+        <v>-16.56047183283697</v>
       </c>
       <c r="F5">
-        <v>2.290381877611943</v>
+        <v>2.327209435605604</v>
       </c>
       <c r="G5">
-        <v>-14.3213394240496</v>
+        <v>-12.81885982798079</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.41679697307471</v>
       </c>
       <c r="E6">
-        <v>-19.11211765337381</v>
+        <v>-17.30954918059438</v>
       </c>
       <c r="F6">
-        <v>2.566408806837989</v>
+        <v>2.452844606118593</v>
       </c>
       <c r="G6">
-        <v>-13.58551672551187</v>
+        <v>-12.22495590004369</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.80572670466367</v>
       </c>
       <c r="E7">
-        <v>-21.45209090552943</v>
+        <v>-17.8206807451297</v>
       </c>
       <c r="F7">
-        <v>1.26553898074684</v>
+        <v>2.55234809854287</v>
       </c>
       <c r="G7">
-        <v>-13.29350885911274</v>
+        <v>-12.30251981647337</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.20014152200648</v>
       </c>
       <c r="E8">
-        <v>-21.12932824063171</v>
+        <v>-18.25467471572898</v>
       </c>
       <c r="F8">
-        <v>2.410897737575632</v>
+        <v>2.586389028593513</v>
       </c>
       <c r="G8">
-        <v>-12.60795082618771</v>
+        <v>-11.83696270337997</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.622719923628846</v>
       </c>
       <c r="E9">
-        <v>-21.92129164852929</v>
+        <v>-18.493949526575</v>
       </c>
       <c r="F9">
-        <v>1.711573408784234</v>
+        <v>2.63056586218481</v>
       </c>
       <c r="G9">
-        <v>-11.89682185536502</v>
+        <v>-11.35757256007057</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.064923824427495</v>
       </c>
       <c r="E10">
-        <v>-21.58192859796622</v>
+        <v>-20.06893032517648</v>
       </c>
       <c r="F10">
-        <v>1.664286883962827</v>
+        <v>2.720150483327966</v>
       </c>
       <c r="G10">
-        <v>-11.52956188687164</v>
+        <v>-11.24533795547091</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.528102797769726</v>
       </c>
       <c r="E11">
-        <v>-21.14785986956309</v>
+        <v>-19.98398469394977</v>
       </c>
       <c r="F11">
-        <v>3.019881974152522</v>
+        <v>2.991019997104182</v>
       </c>
       <c r="G11">
-        <v>-11.53346886615224</v>
+        <v>-10.57310385756662</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.013646955244175</v>
       </c>
       <c r="E12">
-        <v>-22.94032357918922</v>
+        <v>-20.10658333904738</v>
       </c>
       <c r="F12">
-        <v>2.724217767275712</v>
+        <v>3.087564561165659</v>
       </c>
       <c r="G12">
-        <v>-11.5521356899787</v>
+        <v>-10.15344232901271</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.506986517213677</v>
       </c>
       <c r="E13">
-        <v>-23.97027845563345</v>
+        <v>-21.18095681061065</v>
       </c>
       <c r="F13">
-        <v>2.932563766223427</v>
+        <v>3.346787229258513</v>
       </c>
       <c r="G13">
-        <v>-11.6136226412163</v>
+        <v>-9.488715427180175</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.018061241432333</v>
       </c>
       <c r="E14">
-        <v>-24.73171991350486</v>
+        <v>-22.49287320389749</v>
       </c>
       <c r="F14">
-        <v>3.260249343422855</v>
+        <v>3.459914051989231</v>
       </c>
       <c r="G14">
-        <v>-9.585108033600964</v>
+        <v>-9.43650575684709</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.536518659749841</v>
       </c>
       <c r="E15">
-        <v>-26.48916789845136</v>
+        <v>-22.79388134787576</v>
       </c>
       <c r="F15">
-        <v>2.191272688071399</v>
+        <v>3.883577589946621</v>
       </c>
       <c r="G15">
-        <v>-9.78146605041548</v>
+        <v>-9.060400585679016</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.060693737708848</v>
       </c>
       <c r="E16">
-        <v>-26.30248935582297</v>
+        <v>-23.6734899743612</v>
       </c>
       <c r="F16">
-        <v>2.977027214936093</v>
+        <v>3.921689117414621</v>
       </c>
       <c r="G16">
-        <v>-10.06814538710415</v>
+        <v>-8.331445450788205</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.591501964098883</v>
       </c>
       <c r="E17">
-        <v>-26.48753153318938</v>
+        <v>-25.17696493358311</v>
       </c>
       <c r="F17">
-        <v>3.06523343272099</v>
+        <v>4.264457608284223</v>
       </c>
       <c r="G17">
-        <v>-10.26835947367974</v>
+        <v>-8.22101225995641</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.116828589871229</v>
       </c>
       <c r="E18">
-        <v>-26.7305027021145</v>
+        <v>-24.65931698047913</v>
       </c>
       <c r="F18">
-        <v>3.673279957397911</v>
+        <v>4.623394174121666</v>
       </c>
       <c r="G18">
-        <v>-8.876563699923478</v>
+        <v>-7.623085174604394</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.644196691964654</v>
       </c>
       <c r="E19">
-        <v>-25.48056052821675</v>
+        <v>-25.46614057849694</v>
       </c>
       <c r="F19">
-        <v>3.560239284877085</v>
+        <v>4.595496416730183</v>
       </c>
       <c r="G19">
-        <v>-9.16839011957353</v>
+        <v>-7.523516597388515</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.170598385308654</v>
       </c>
       <c r="E20">
-        <v>-27.04632119767711</v>
+        <v>-26.41105845306531</v>
       </c>
       <c r="F20">
-        <v>4.181453537788907</v>
+        <v>4.965697122510893</v>
       </c>
       <c r="G20">
-        <v>-8.443220564339835</v>
+        <v>-7.565849820933417</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.70364740239125</v>
       </c>
       <c r="E21">
-        <v>-29.33034031025898</v>
+        <v>-27.22438598001781</v>
       </c>
       <c r="F21">
-        <v>4.797468956880759</v>
+        <v>4.930355655637856</v>
       </c>
       <c r="G21">
-        <v>-8.319650106725556</v>
+        <v>-7.349721940702695</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.260752110586834</v>
       </c>
       <c r="E22">
-        <v>-28.8580246587655</v>
+        <v>-27.18073572899386</v>
       </c>
       <c r="F22">
-        <v>4.416701596509938</v>
+        <v>5.126337442731385</v>
       </c>
       <c r="G22">
-        <v>-8.733376107451575</v>
+        <v>-7.187824447118578</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.851558398180436</v>
       </c>
       <c r="E23">
-        <v>-28.35566882975954</v>
+        <v>-27.1500974890506</v>
       </c>
       <c r="F23">
-        <v>4.410820187950062</v>
+        <v>4.97947287241945</v>
       </c>
       <c r="G23">
-        <v>-8.579960923043984</v>
+        <v>-6.837642664367962</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.500671617529848</v>
       </c>
       <c r="E24">
-        <v>-28.68371230285679</v>
+        <v>-28.19065551400712</v>
       </c>
       <c r="F24">
-        <v>3.88936787809219</v>
+        <v>5.258674105533023</v>
       </c>
       <c r="G24">
-        <v>-6.535801428466399</v>
+        <v>-6.725845359487309</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.222678378239021</v>
       </c>
       <c r="E25">
-        <v>-31.38770622121098</v>
+        <v>-29.16740982998596</v>
       </c>
       <c r="F25">
-        <v>4.556021396517176</v>
+        <v>5.366284001361096</v>
       </c>
       <c r="G25">
-        <v>-8.795184180273885</v>
+        <v>-6.639964916162637</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.02833729895975</v>
       </c>
       <c r="E26">
-        <v>-30.65046967894067</v>
+        <v>-28.61111416889878</v>
       </c>
       <c r="F26">
-        <v>4.792477214911489</v>
+        <v>5.226482091525429</v>
       </c>
       <c r="G26">
-        <v>-8.061749007664726</v>
+        <v>-6.577254831084096</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.929621909154921</v>
       </c>
       <c r="E27">
-        <v>-30.76616984002774</v>
+        <v>-28.23045158492162</v>
       </c>
       <c r="F27">
-        <v>3.986315028711427</v>
+        <v>5.055641255106864</v>
       </c>
       <c r="G27">
-        <v>-7.873238889091096</v>
+        <v>-6.676416132143761</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.921473471527035</v>
       </c>
       <c r="E28">
-        <v>-29.52603339806791</v>
+        <v>-28.87454198020435</v>
       </c>
       <c r="F28">
-        <v>4.523970204968057</v>
+        <v>5.296449315835486</v>
       </c>
       <c r="G28">
-        <v>-7.382251818307966</v>
+        <v>-5.909037363733241</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.00185311168861</v>
       </c>
       <c r="E29">
-        <v>-30.82491701421744</v>
+        <v>-29.34673095875242</v>
       </c>
       <c r="F29">
-        <v>4.431164891362817</v>
+        <v>5.062950769069167</v>
       </c>
       <c r="G29">
-        <v>-7.330070866165386</v>
+        <v>-5.983947458286055</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.158477185441923</v>
       </c>
       <c r="E30">
-        <v>-30.33709534824272</v>
+        <v>-28.47410180389835</v>
       </c>
       <c r="F30">
-        <v>4.821680479329783</v>
+        <v>4.930160160930795</v>
       </c>
       <c r="G30">
-        <v>-7.897031909922206</v>
+        <v>-6.436595744748685</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.371606481618147</v>
       </c>
       <c r="E31">
-        <v>-30.22102970455906</v>
+        <v>-28.30762863436525</v>
       </c>
       <c r="F31">
-        <v>4.037743390546832</v>
+        <v>4.945016101932602</v>
       </c>
       <c r="G31">
-        <v>-7.401594824983525</v>
+        <v>-5.93091279266218</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.627322302263325</v>
       </c>
       <c r="E32">
-        <v>-29.18395207069275</v>
+        <v>-28.13264138161625</v>
       </c>
       <c r="F32">
-        <v>3.939669660259787</v>
+        <v>4.660203508032464</v>
       </c>
       <c r="G32">
-        <v>-6.962616397199963</v>
+        <v>-6.131196063969435</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.902120247349993</v>
       </c>
       <c r="E33">
-        <v>-31.29470751322542</v>
+        <v>-28.66442686606995</v>
       </c>
       <c r="F33">
-        <v>4.171425322010616</v>
+        <v>4.825495939587078</v>
       </c>
       <c r="G33">
-        <v>-7.805411744613973</v>
+        <v>-5.828751746067326</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.178707414988264</v>
       </c>
       <c r="E34">
-        <v>-30.35661336486375</v>
+        <v>-28.255497525816</v>
       </c>
       <c r="F34">
-        <v>4.783616997171146</v>
+        <v>4.717231633510793</v>
       </c>
       <c r="G34">
-        <v>-7.338132845462743</v>
+        <v>-5.884859258074941</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.441757871243346</v>
       </c>
       <c r="E35">
-        <v>-29.40191260101975</v>
+        <v>-28.06784297852628</v>
       </c>
       <c r="F35">
-        <v>4.201533163632766</v>
+        <v>4.856844675578622</v>
       </c>
       <c r="G35">
-        <v>-6.967809168191688</v>
+        <v>-6.192094292301744</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.674485671718196</v>
       </c>
       <c r="E36">
-        <v>-29.3940422655592</v>
+        <v>-26.9048046749949</v>
       </c>
       <c r="F36">
-        <v>4.487334828211846</v>
+        <v>5.083802433332436</v>
       </c>
       <c r="G36">
-        <v>-7.575365984968025</v>
+        <v>-5.81234582705677</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.873747842564588</v>
       </c>
       <c r="E37">
-        <v>-29.43894263319192</v>
+        <v>-27.48287769966381</v>
       </c>
       <c r="F37">
-        <v>4.55196902318268</v>
+        <v>5.004582345133108</v>
       </c>
       <c r="G37">
-        <v>-7.559928652200773</v>
+        <v>-6.268555169141679</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.034665349973687</v>
       </c>
       <c r="E38">
-        <v>-27.88305622365634</v>
+        <v>-26.85930209172008</v>
       </c>
       <c r="F38">
-        <v>4.453749500232743</v>
+        <v>5.163668648105948</v>
       </c>
       <c r="G38">
-        <v>-7.536583374067037</v>
+        <v>-6.019354376430734</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.160218444952286</v>
       </c>
       <c r="E39">
-        <v>-26.81026097239651</v>
+        <v>-26.10909507048233</v>
       </c>
       <c r="F39">
-        <v>4.139917539477734</v>
+        <v>5.399040961937399</v>
       </c>
       <c r="G39">
-        <v>-8.217747523845222</v>
+        <v>-6.427212728688224</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.259535271687676</v>
       </c>
       <c r="E40">
-        <v>-28.02057735704406</v>
+        <v>-25.82131075136231</v>
       </c>
       <c r="F40">
-        <v>4.479886148525873</v>
+        <v>5.449462029010999</v>
       </c>
       <c r="G40">
-        <v>-7.920232291731135</v>
+        <v>-6.443049505377918</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.336492873363364</v>
       </c>
       <c r="E41">
-        <v>-27.99095250066406</v>
+        <v>-26.16662950696518</v>
       </c>
       <c r="F41">
-        <v>4.415006756803811</v>
+        <v>5.225658694327046</v>
       </c>
       <c r="G41">
-        <v>-8.024192141349266</v>
+        <v>-6.848192683260651</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.406696222618665</v>
       </c>
       <c r="E42">
-        <v>-26.42488449356566</v>
+        <v>-25.05385544349254</v>
       </c>
       <c r="F42">
-        <v>4.356366628359633</v>
+        <v>5.33309131953092</v>
       </c>
       <c r="G42">
-        <v>-8.654553812128977</v>
+        <v>-6.765121401116017</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.477447812157419</v>
       </c>
       <c r="E43">
-        <v>-27.10215697072811</v>
+        <v>-24.741093711465</v>
       </c>
       <c r="F43">
-        <v>4.313785230386127</v>
+        <v>5.551150754643861</v>
       </c>
       <c r="G43">
-        <v>-8.361022576260929</v>
+        <v>-6.630383483513252</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.557990287262212</v>
       </c>
       <c r="E44">
-        <v>-26.89116968221549</v>
+        <v>-23.76331978210592</v>
       </c>
       <c r="F44">
-        <v>4.271458969572684</v>
+        <v>5.597025741410897</v>
       </c>
       <c r="G44">
-        <v>-8.551114806056773</v>
+        <v>-6.578523652955377</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.659318559827961</v>
       </c>
       <c r="E45">
-        <v>-25.26654554864833</v>
+        <v>-23.8449303846388</v>
       </c>
       <c r="F45">
-        <v>4.788033852162872</v>
+        <v>5.877991397092434</v>
       </c>
       <c r="G45">
-        <v>-7.997848423052637</v>
+        <v>-6.872981703153271</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.779290806804689</v>
       </c>
       <c r="E46">
-        <v>-23.51938922136477</v>
+        <v>-23.35759672099474</v>
       </c>
       <c r="F46">
-        <v>4.445381332729663</v>
+        <v>5.478554292197318</v>
       </c>
       <c r="G46">
-        <v>-8.57891923595213</v>
+        <v>-6.789826877181722</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.926414599747575</v>
       </c>
       <c r="E47">
-        <v>-25.64265205980216</v>
+        <v>-22.78501424169725</v>
       </c>
       <c r="F47">
-        <v>5.227935047949939</v>
+        <v>5.745730944091854</v>
       </c>
       <c r="G47">
-        <v>-8.00599133543232</v>
+        <v>-6.837136179917286</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.09646123954148</v>
       </c>
       <c r="E48">
-        <v>-24.58223753150164</v>
+        <v>-22.35451312182215</v>
       </c>
       <c r="F48">
-        <v>4.845371787049848</v>
+        <v>5.629961629346206</v>
       </c>
       <c r="G48">
-        <v>-8.504206252615946</v>
+        <v>-7.025470073231016</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.286026484671575</v>
       </c>
       <c r="E49">
-        <v>-22.99546991916029</v>
+        <v>-22.12281792164394</v>
       </c>
       <c r="F49">
-        <v>4.846544755292213</v>
+        <v>5.659834214625962</v>
       </c>
       <c r="G49">
-        <v>-8.622593076844568</v>
+        <v>-6.74214684871422</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.495735806833014</v>
       </c>
       <c r="E50">
-        <v>-22.59046121039699</v>
+        <v>-21.67714512079924</v>
       </c>
       <c r="F50">
-        <v>4.392715389994476</v>
+        <v>5.856912760160798</v>
       </c>
       <c r="G50">
-        <v>-8.297174206540662</v>
+        <v>-7.00901716081782</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.713065154832695</v>
       </c>
       <c r="E51">
-        <v>-22.5706919244908</v>
+        <v>-20.39271468006012</v>
       </c>
       <c r="F51">
-        <v>4.627256022953516</v>
+        <v>5.637090559214699</v>
       </c>
       <c r="G51">
-        <v>-7.842250656166876</v>
+        <v>-7.183454060673054</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.939876615355076</v>
       </c>
       <c r="E52">
-        <v>-22.13008604146239</v>
+        <v>-19.57873509892962</v>
       </c>
       <c r="F52">
-        <v>4.465335046728297</v>
+        <v>6.107846784021241</v>
       </c>
       <c r="G52">
-        <v>-8.772029486495303</v>
+        <v>-6.917163333868682</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.167760249588534</v>
       </c>
       <c r="E53">
-        <v>-22.86314445313993</v>
+        <v>-19.87127899822789</v>
       </c>
       <c r="F53">
-        <v>5.032475132320173</v>
+        <v>5.823539494236812</v>
       </c>
       <c r="G53">
-        <v>-7.987462881069188</v>
+        <v>-7.365811959617727</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.390512481778287</v>
       </c>
       <c r="E54">
-        <v>-21.84763859889478</v>
+        <v>-19.51395330868495</v>
       </c>
       <c r="F54">
-        <v>4.641974454966459</v>
+        <v>5.530837529192412</v>
       </c>
       <c r="G54">
-        <v>-8.305298843708206</v>
+        <v>-7.347991017038787</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.610434027063419</v>
       </c>
       <c r="E55">
-        <v>-21.49237705538027</v>
+        <v>-19.11065572298747</v>
       </c>
       <c r="F55">
-        <v>4.754562838885356</v>
+        <v>5.93420772251602</v>
       </c>
       <c r="G55">
-        <v>-9.038689633659317</v>
+        <v>-7.434693844909659</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.81733059781036</v>
       </c>
       <c r="E56">
-        <v>-21.98718234619769</v>
+        <v>-18.74032632878648</v>
       </c>
       <c r="F56">
-        <v>4.443638447714172</v>
+        <v>5.584843770385328</v>
       </c>
       <c r="G56">
-        <v>-8.62964339261287</v>
+        <v>-7.519195815090223</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.01856738077368</v>
       </c>
       <c r="E57">
-        <v>-20.80366663422925</v>
+        <v>-17.30187819927742</v>
       </c>
       <c r="F57">
-        <v>4.172228838391331</v>
+        <v>5.74771239891935</v>
       </c>
       <c r="G57">
-        <v>-8.844306645127977</v>
+        <v>-7.588947078330997</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.212714512587978</v>
       </c>
       <c r="E58">
-        <v>-18.55423338895489</v>
+        <v>-17.81993316709123</v>
       </c>
       <c r="F58">
-        <v>4.773978114072171</v>
+        <v>5.649855700891839</v>
       </c>
       <c r="G58">
-        <v>-8.650675551038878</v>
+        <v>-7.284288849015622</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.399148371024483</v>
       </c>
       <c r="E59">
-        <v>-20.44219603978413</v>
+        <v>-17.77473376824312</v>
       </c>
       <c r="F59">
-        <v>4.781133551697553</v>
+        <v>5.816809837456468</v>
       </c>
       <c r="G59">
-        <v>-9.186854610694178</v>
+        <v>-7.613172177391936</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.58746948553991</v>
       </c>
       <c r="E60">
-        <v>-20.30893194800435</v>
+        <v>-17.24069309004004</v>
       </c>
       <c r="F60">
-        <v>3.932452923446597</v>
+        <v>5.726935287722333</v>
       </c>
       <c r="G60">
-        <v>-8.536219202792177</v>
+        <v>-7.991462541782774</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.770861130142045</v>
       </c>
       <c r="E61">
-        <v>-20.40972623364662</v>
+        <v>-16.96602461228383</v>
       </c>
       <c r="F61">
-        <v>4.148902012328497</v>
+        <v>5.341570488265975</v>
       </c>
       <c r="G61">
-        <v>-7.718994793275827</v>
+        <v>-8.133211613984974</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.959636005676189</v>
       </c>
       <c r="E62">
-        <v>-19.93238934966142</v>
+        <v>-16.50405461020051</v>
       </c>
       <c r="F62">
-        <v>4.133754486000906</v>
+        <v>5.37143976007612</v>
       </c>
       <c r="G62">
-        <v>-9.069210543301727</v>
+        <v>-7.971598691561288</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.153087485874558</v>
       </c>
       <c r="E63">
-        <v>-18.95144652006149</v>
+        <v>-15.91690681878684</v>
       </c>
       <c r="F63">
-        <v>3.875259124487709</v>
+        <v>5.41852581998605</v>
       </c>
       <c r="G63">
-        <v>-8.9821422111881</v>
+        <v>-7.985046636950113</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.347318111166382</v>
       </c>
       <c r="E64">
-        <v>-19.58979094747632</v>
+        <v>-16.24928416790155</v>
       </c>
       <c r="F64">
-        <v>3.964376546415685</v>
+        <v>5.277811049272497</v>
       </c>
       <c r="G64">
-        <v>-10.09193710256297</v>
+        <v>-8.340904178441809</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.548827091219938</v>
       </c>
       <c r="E65">
-        <v>-18.97393200617411</v>
+        <v>-15.2736740616427</v>
       </c>
       <c r="F65">
-        <v>3.847170842593583</v>
+        <v>5.106925481014182</v>
       </c>
       <c r="G65">
-        <v>-9.850342714218231</v>
+        <v>-8.65446765755747</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.744491789824325</v>
       </c>
       <c r="E66">
-        <v>-18.86249719311764</v>
+        <v>-15.49785194932297</v>
       </c>
       <c r="F66">
-        <v>3.821791322106612</v>
+        <v>5.211067830894136</v>
       </c>
       <c r="G66">
-        <v>-8.977064312958383</v>
+        <v>-8.578617694951856</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.939103017263154</v>
       </c>
       <c r="E67">
-        <v>-19.23527698200028</v>
+        <v>-15.48028801863027</v>
       </c>
       <c r="F67">
-        <v>4.698629815113527</v>
+        <v>5.012624135879486</v>
       </c>
       <c r="G67">
-        <v>-11.02765407146388</v>
+        <v>-8.509861125400297</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.127195358064045</v>
       </c>
       <c r="E68">
-        <v>-18.5225693058144</v>
+        <v>-15.19100439022199</v>
       </c>
       <c r="F68">
-        <v>3.873378730483354</v>
+        <v>5.233327719742164</v>
       </c>
       <c r="G68">
-        <v>-10.00506327092138</v>
+        <v>-8.839859241717017</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.299289467942531</v>
       </c>
       <c r="E69">
-        <v>-18.18025332199938</v>
+        <v>-15.20718945475484</v>
       </c>
       <c r="F69">
-        <v>4.69816592936796</v>
+        <v>5.331618482288742</v>
       </c>
       <c r="G69">
-        <v>-9.707007614676929</v>
+        <v>-8.77906935928524</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.45877980050629</v>
       </c>
       <c r="E70">
-        <v>-16.94704443652937</v>
+        <v>-15.29789143687777</v>
       </c>
       <c r="F70">
-        <v>3.770608157022436</v>
+        <v>5.223562924797963</v>
       </c>
       <c r="G70">
-        <v>-11.19897374227733</v>
+        <v>-9.189619389216167</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.590687618387928</v>
       </c>
       <c r="E71">
-        <v>-17.07458540310353</v>
+        <v>-14.58407070005684</v>
       </c>
       <c r="F71">
-        <v>4.851963934841327</v>
+        <v>5.127966013045289</v>
       </c>
       <c r="G71">
-        <v>-9.738578043644967</v>
+        <v>-8.475176078135062</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.698289825167764</v>
       </c>
       <c r="E72">
-        <v>-17.3689691750187</v>
+        <v>-14.93581447357922</v>
       </c>
       <c r="F72">
-        <v>3.724068819598354</v>
+        <v>4.948828248720285</v>
       </c>
       <c r="G72">
-        <v>-11.1824124839636</v>
+        <v>-8.75329869942636</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.776884685585465</v>
       </c>
       <c r="E73">
-        <v>-18.94307779924196</v>
+        <v>-15.17934217282187</v>
       </c>
       <c r="F73">
-        <v>3.519370950692568</v>
+        <v>5.198846098233232</v>
       </c>
       <c r="G73">
-        <v>-9.034756546932805</v>
+        <v>-8.789325669411427</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.818635450265749</v>
       </c>
       <c r="E74">
-        <v>-17.05387333822661</v>
+        <v>-14.89685319814101</v>
       </c>
       <c r="F74">
-        <v>4.010017933575132</v>
+        <v>5.043744242467858</v>
       </c>
       <c r="G74">
-        <v>-10.28695189128536</v>
+        <v>-9.070116471674844</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.830260739794547</v>
       </c>
       <c r="E75">
-        <v>-18.01101411372394</v>
+        <v>-14.81146317330253</v>
       </c>
       <c r="F75">
-        <v>4.544662822689989</v>
+        <v>5.0942961915911</v>
       </c>
       <c r="G75">
-        <v>-9.694551752232728</v>
+        <v>-8.777801842786253</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.800465040075716</v>
       </c>
       <c r="E76">
-        <v>-17.05117790407679</v>
+        <v>-15.54194659395867</v>
       </c>
       <c r="F76">
-        <v>3.951311535738731</v>
+        <v>5.0282222940742</v>
       </c>
       <c r="G76">
-        <v>-10.22663194287998</v>
+        <v>-8.360335950433466</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.734467620045233</v>
       </c>
       <c r="E77">
-        <v>-17.80959997731506</v>
+        <v>-15.79319095984285</v>
       </c>
       <c r="F77">
-        <v>4.05162351474814</v>
+        <v>5.23967964098683</v>
       </c>
       <c r="G77">
-        <v>-9.745338566763655</v>
+        <v>-8.545279791895636</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.629498881433035</v>
       </c>
       <c r="E78">
-        <v>-18.56708342479391</v>
+        <v>-15.66047093874663</v>
       </c>
       <c r="F78">
-        <v>4.370220244804052</v>
+        <v>4.902176253329422</v>
       </c>
       <c r="G78">
-        <v>-9.354478772538902</v>
+        <v>-8.874049552882235</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.478944933647883</v>
       </c>
       <c r="E79">
-        <v>-20.25161763172172</v>
+        <v>-16.61545619756638</v>
       </c>
       <c r="F79">
-        <v>3.905371936314276</v>
+        <v>4.604066705879547</v>
       </c>
       <c r="G79">
-        <v>-9.419042486277133</v>
+        <v>-8.617153590488984</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.290128270604805</v>
       </c>
       <c r="E80">
-        <v>-18.41900067500715</v>
+        <v>-16.99078605820246</v>
       </c>
       <c r="F80">
-        <v>3.409266012247263</v>
+        <v>4.880391847370601</v>
       </c>
       <c r="G80">
-        <v>-9.139128894196332</v>
+        <v>-8.163162075934226</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.05387356340114</v>
       </c>
       <c r="E81">
-        <v>-20.94317715584157</v>
+        <v>-16.63170771348043</v>
       </c>
       <c r="F81">
-        <v>4.001457584834602</v>
+        <v>5.064163498946866</v>
       </c>
       <c r="G81">
-        <v>-9.387862363625468</v>
+        <v>-8.060781726793719</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.777980471899744</v>
       </c>
       <c r="E82">
-        <v>-20.07270974748208</v>
+        <v>-17.79244306133219</v>
       </c>
       <c r="F82">
-        <v>3.7347050570503</v>
+        <v>4.530845654411293</v>
       </c>
       <c r="G82">
-        <v>-8.436822934719311</v>
+        <v>-8.051846453430633</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.464268332817133</v>
       </c>
       <c r="E83">
-        <v>-19.68392763536488</v>
+        <v>-19.12937009321715</v>
       </c>
       <c r="F83">
-        <v>3.808187872617838</v>
+        <v>4.751539297865138</v>
       </c>
       <c r="G83">
-        <v>-8.745303294116075</v>
+        <v>-7.524177115770067</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.11221531040764</v>
       </c>
       <c r="E84">
-        <v>-21.50085791290557</v>
+        <v>-19.62319107295059</v>
       </c>
       <c r="F84">
-        <v>3.919518794819286</v>
+        <v>4.555984948351453</v>
       </c>
       <c r="G84">
-        <v>-8.859087375630565</v>
+        <v>-6.79265953506308</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.735656258563207</v>
       </c>
       <c r="E85">
-        <v>-23.18677098599322</v>
+        <v>-20.68856868878428</v>
       </c>
       <c r="F85">
-        <v>3.199752015261601</v>
+        <v>4.639638458890563</v>
       </c>
       <c r="G85">
-        <v>-9.201743687097297</v>
+        <v>-7.472735004346771</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.333784169765804</v>
       </c>
       <c r="E86">
-        <v>-24.00991255130629</v>
+        <v>-21.54178781051176</v>
       </c>
       <c r="F86">
-        <v>3.795432671349531</v>
+        <v>4.583935721256713</v>
       </c>
       <c r="G86">
-        <v>-7.910128710163526</v>
+        <v>-7.025788584071132</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.922171864598013</v>
       </c>
       <c r="E87">
-        <v>-23.53316127011789</v>
+        <v>-22.20537960957021</v>
       </c>
       <c r="F87">
-        <v>3.555620308239074</v>
+        <v>4.519251824241712</v>
       </c>
       <c r="G87">
-        <v>-8.928405255269215</v>
+        <v>-6.269865762926417</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.512292057474583</v>
       </c>
       <c r="E88">
-        <v>-27.04564007101984</v>
+        <v>-23.54197853776051</v>
       </c>
       <c r="F88">
-        <v>3.522452477430982</v>
+        <v>4.234430946667546</v>
       </c>
       <c r="G88">
-        <v>-8.26739735910672</v>
+        <v>-6.472107092677009</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.112165439966864</v>
       </c>
       <c r="E89">
-        <v>-28.10377656290869</v>
+        <v>-25.39277410044385</v>
       </c>
       <c r="F89">
-        <v>3.567928191109869</v>
+        <v>4.138855572467345</v>
       </c>
       <c r="G89">
-        <v>-8.330842368787659</v>
+        <v>-6.069428457688287</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.742671051675656</v>
       </c>
       <c r="E90">
-        <v>-27.67936612744145</v>
+        <v>-26.65520498079536</v>
       </c>
       <c r="F90">
-        <v>3.290507947912315</v>
+        <v>3.999908537791367</v>
       </c>
       <c r="G90">
-        <v>-8.434525479479133</v>
+        <v>-6.076997006257923</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.406655627098018</v>
       </c>
       <c r="E91">
-        <v>-30.65269372360511</v>
+        <v>-27.72180779396987</v>
       </c>
       <c r="F91">
-        <v>3.482677588218162</v>
+        <v>4.023538546323626</v>
       </c>
       <c r="G91">
-        <v>-8.460621177039604</v>
+        <v>-6.346720862199611</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.115338170045994</v>
       </c>
       <c r="E92">
-        <v>-30.97409828839962</v>
+        <v>-29.5074540072063</v>
       </c>
       <c r="F92">
-        <v>2.759897208049092</v>
+        <v>3.95811077538091</v>
       </c>
       <c r="G92">
-        <v>-7.780053582400489</v>
+        <v>-5.615331207977588</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.870787176498441</v>
       </c>
       <c r="E93">
-        <v>-32.55307447629558</v>
+        <v>-31.27474510299263</v>
       </c>
       <c r="F93">
-        <v>3.07190013357872</v>
+        <v>3.706141292266967</v>
       </c>
       <c r="G93">
-        <v>-8.041447857724229</v>
+        <v>-6.215029683534675</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.664342366396582</v>
       </c>
       <c r="E94">
-        <v>-33.71584697430217</v>
+        <v>-33.04543144903703</v>
       </c>
       <c r="F94">
-        <v>2.953173547205078</v>
+        <v>3.358263431256898</v>
       </c>
       <c r="G94">
-        <v>-8.499576097083606</v>
+        <v>-5.970901567564262</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.496303350944643</v>
       </c>
       <c r="E95">
-        <v>-35.1974469694762</v>
+        <v>-35.3894790015023</v>
       </c>
       <c r="F95">
-        <v>2.685972044288458</v>
+        <v>3.348912820014097</v>
       </c>
       <c r="G95">
-        <v>-7.718890363492182</v>
+        <v>-5.972003301781712</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.348573113946685</v>
       </c>
       <c r="E96">
-        <v>-37.75595804833298</v>
+        <v>-36.74650965280509</v>
       </c>
       <c r="F96">
-        <v>2.222459064051995</v>
+        <v>2.720647503769646</v>
       </c>
       <c r="G96">
-        <v>-8.13378597779502</v>
+        <v>-5.278469444130832</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.213187443196698</v>
       </c>
       <c r="E97">
-        <v>-42.13209922083868</v>
+        <v>-38.76924193451935</v>
       </c>
       <c r="F97">
-        <v>2.307524112645476</v>
+        <v>2.654094809893928</v>
       </c>
       <c r="G97">
-        <v>-7.358303458173684</v>
+        <v>-5.996685281146097</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.073728874563479</v>
       </c>
       <c r="E98">
-        <v>-41.3669427154372</v>
+        <v>-40.88826019098277</v>
       </c>
       <c r="F98">
-        <v>1.350509595456402</v>
+        <v>2.309026771114155</v>
       </c>
       <c r="G98">
-        <v>-7.041468716085358</v>
+        <v>-6.105190437097356</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.918559748087273</v>
       </c>
       <c r="E99">
-        <v>-43.90750361494808</v>
+        <v>-42.56534976661082</v>
       </c>
       <c r="F99">
-        <v>0.9498564472139761</v>
+        <v>1.797662319487575</v>
       </c>
       <c r="G99">
-        <v>-7.279325823547916</v>
+        <v>-5.686844723817363</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.735145562956748</v>
       </c>
       <c r="E100">
-        <v>-47.13690991497802</v>
+        <v>-45.54870010000413</v>
       </c>
       <c r="F100">
-        <v>0.9153963632575167</v>
+        <v>1.734464513593195</v>
       </c>
       <c r="G100">
-        <v>-6.987345369966989</v>
+        <v>-6.094128712264809</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.528135361943373</v>
       </c>
       <c r="E101">
-        <v>-48.77232097665858</v>
+        <v>-47.45204832218619</v>
       </c>
       <c r="F101">
-        <v>1.413795208295479</v>
+        <v>1.398183796222319</v>
       </c>
       <c r="G101">
-        <v>-8.382740055142104</v>
+        <v>-6.245765979605851</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.274569868988078</v>
       </c>
       <c r="E102">
-        <v>-51.03311429320918</v>
+        <v>-50.05671403849578</v>
       </c>
       <c r="F102">
-        <v>0.3379033418654526</v>
+        <v>1.188341765745148</v>
       </c>
       <c r="G102">
-        <v>-7.988208248649951</v>
+        <v>-6.077641860171929</v>
       </c>
     </row>
   </sheetData>
